--- a/arduino/PINS.xlsx
+++ b/arduino/PINS.xlsx
@@ -1,30 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VLR\Desktop\HYDRO PULSE\hydropulse\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\HYDRO PULSE\hydropulse\arduino\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51BDB20-4700-4367-94CC-5E975ADDF142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12480"/>
+    <workbookView xWindow="7800" yWindow="5220" windowWidth="14040" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>MISO</t>
   </si>
@@ -66,12 +81,33 @@
   </si>
   <si>
     <t>D9</t>
+  </si>
+  <si>
+    <t>VCC</t>
+  </si>
+  <si>
+    <t>5V</t>
+  </si>
+  <si>
+    <t>Trig</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>Echo</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>GND</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -386,8 +422,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -454,6 +490,38 @@
         <v>13</v>
       </c>
     </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
